--- a/model/Inputs/inputs_RE.xlsx
+++ b/model/Inputs/inputs_RE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF1C25D0-4CB7-4BC2-9C33-1D8953AC8A11}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495A37BE-6FBB-4E3C-92A2-55B475ABE098}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -1621,153 +1621,153 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.2623351352601862</v>
+        <v>0.50966710862198827</v>
       </c>
       <c r="C2">
-        <v>0.17062120330461161</v>
+        <v>0.5378994808540265</v>
       </c>
       <c r="D2">
-        <v>0.2092049542430571</v>
+        <v>0.53090703423607699</v>
       </c>
       <c r="E2">
-        <v>0.28747276823387014</v>
+        <v>0.53124301708715971</v>
       </c>
       <c r="F2">
-        <v>0.36604134920128423</v>
+        <v>0.52153379679324718</v>
       </c>
       <c r="G2">
-        <v>0.41222889257948481</v>
+        <v>0.49426688993448104</v>
       </c>
       <c r="H2">
-        <v>0.36872864366248936</v>
+        <v>0.42588406065382994</v>
       </c>
       <c r="I2">
-        <v>0.34093467439274378</v>
+        <v>0.38927000806723039</v>
       </c>
       <c r="J2">
-        <v>0.29284143627333531</v>
+        <v>0.32784201041527922</v>
       </c>
       <c r="K2">
-        <v>0.37229578188674872</v>
+        <v>0.39403786103913829</v>
       </c>
       <c r="L2">
-        <v>0.40984403001373088</v>
+        <v>0.42387390011083459</v>
       </c>
       <c r="M2">
-        <v>0.40508530223820943</v>
+        <v>0.41429178637998687</v>
       </c>
       <c r="N2">
-        <v>0.40344423654076739</v>
+        <v>0.41261342373487581</v>
       </c>
       <c r="O2">
-        <v>0.38165770479616301</v>
+        <v>0.41384570399583948</v>
       </c>
       <c r="P2">
-        <v>0.37891608840766111</v>
+        <v>0.41587988599549158</v>
       </c>
       <c r="Q2">
-        <v>0.37389510552131089</v>
+        <v>0.39982959439825999</v>
       </c>
       <c r="R2">
-        <v>0.38774062129651121</v>
+        <v>0.38773501471725841</v>
       </c>
       <c r="S2">
         <v>0.3186474998936335</v>
       </c>
       <c r="T2">
-        <v>0.24380642028312829</v>
+        <v>0.25054140426885008</v>
       </c>
       <c r="U2">
-        <v>0.25395866140635881</v>
+        <v>0.27056497061016371</v>
       </c>
       <c r="V2">
-        <v>0.29588047973401582</v>
+        <v>0.36064017729795278</v>
       </c>
       <c r="W2">
-        <v>0.30127927607913685</v>
+        <v>0.39697265447803048</v>
       </c>
       <c r="X2">
-        <v>0.32115797413359637</v>
+        <v>0.42768970618440738</v>
       </c>
       <c r="Y2">
-        <v>0.36269677918310511</v>
+        <v>0.4793303803666743</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.15382816766586732</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.13016580775379691</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.110470854616307</v>
-      </c>
-      <c r="E3" s="4">
-        <v>9.7743641686650659E-2</v>
-      </c>
-      <c r="F3" s="4">
-        <v>4.7205897881694631E-2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1.289322322142287E-2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>3.3261776673661064E-2</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0.11926557690297759</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0.1072343263734013</v>
-      </c>
-      <c r="K3" s="4">
-        <v>7.2847478437250215E-2</v>
-      </c>
-      <c r="L3" s="4">
-        <v>0.1064278170953237</v>
-      </c>
-      <c r="M3" s="4">
-        <v>5.0854727103317371E-2</v>
-      </c>
-      <c r="N3" s="4">
-        <v>7.3324414341027169E-2</v>
-      </c>
-      <c r="O3" s="4">
-        <v>0.1443651041966427</v>
-      </c>
-      <c r="P3" s="4">
-        <v>9.895206895983219E-2</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>3.5798383593125475E-2</v>
-      </c>
-      <c r="R3" s="4">
-        <v>6.3494702238209397E-2</v>
-      </c>
-      <c r="S3" s="4">
-        <v>1.786535421662672E-2</v>
-      </c>
-      <c r="T3" s="4">
-        <v>2.0976981115107929E-2</v>
-      </c>
-      <c r="U3" s="4">
-        <v>4.7162871828037585E-2</v>
-      </c>
-      <c r="V3" s="4">
-        <v>2.771126862509992E-2</v>
-      </c>
-      <c r="W3" s="4">
-        <v>3.5392782224220605E-2</v>
-      </c>
-      <c r="X3" s="4">
-        <v>4.6282933453237439E-2</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>0.11903915947242209</v>
+      <c r="B3">
+        <v>0.21451117157625252</v>
+      </c>
+      <c r="C3">
+        <v>0.201505708253541</v>
+      </c>
+      <c r="D3">
+        <v>0.18470652041524671</v>
+      </c>
+      <c r="E3">
+        <v>0.18225432239922348</v>
+      </c>
+      <c r="F3">
+        <v>0.1554154603117506</v>
+      </c>
+      <c r="G3">
+        <v>0.1117803120003997</v>
+      </c>
+      <c r="H3">
+        <v>9.0519316070893294E-2</v>
+      </c>
+      <c r="I3">
+        <v>3.6473810596522891E-3</v>
+      </c>
+      <c r="J3">
+        <v>6.4906675934941482E-3</v>
+      </c>
+      <c r="K3">
+        <v>1.3591447442735459E-2</v>
+      </c>
+      <c r="L3">
+        <v>2.2364190957251128E-2</v>
+      </c>
+      <c r="M3">
+        <v>3.1440585337638952E-2</v>
+      </c>
+      <c r="N3">
+        <v>8.5988232895579907E-3</v>
+      </c>
+      <c r="O3">
+        <v>7.2333525303942922E-2</v>
+      </c>
+      <c r="P3">
+        <v>1.866558683208901E-2</v>
+      </c>
+      <c r="Q3">
+        <v>6.6216998886605011E-2</v>
+      </c>
+      <c r="R3">
+        <v>2.0066803971457031E-2</v>
+      </c>
+      <c r="S3">
+        <v>8.3773723157837349E-2</v>
+      </c>
+      <c r="T3">
+        <v>0.1144162737037261</v>
+      </c>
+      <c r="U3">
+        <v>0.16986397859008559</v>
+      </c>
+      <c r="V3">
+        <v>0.20655493073070949</v>
+      </c>
+      <c r="W3">
+        <v>0.22152122671408322</v>
+      </c>
+      <c r="X3">
+        <v>0.20763276923213911</v>
+      </c>
+      <c r="Y3">
+        <v>0.2348585481078552</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -1775,76 +1775,76 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>6.6497939365097805E-2</v>
+        <v>8.005597698503418E-2</v>
       </c>
       <c r="C4">
-        <v>6.0829684742988738E-3</v>
+        <v>7.7211791688954104E-2</v>
       </c>
       <c r="D4">
-        <v>3.6389563487457531E-4</v>
+        <v>5.5918791628873997E-2</v>
       </c>
       <c r="E4">
-        <v>7.0017249552892222E-2</v>
+        <v>1.0642524735926339E-2</v>
       </c>
       <c r="F4">
-        <v>3.6004447702206885E-2</v>
+        <v>3.9543081047258954E-2</v>
       </c>
       <c r="G4">
-        <v>2.9453637187024581E-2</v>
+        <v>8.6450810668165581E-2</v>
       </c>
       <c r="H4">
-        <v>4.8533218738373358E-2</v>
+        <v>0.14607880221876421</v>
       </c>
       <c r="I4">
-        <v>9.2245401997986864E-2</v>
+        <v>0.17308492085455379</v>
       </c>
       <c r="J4">
-        <v>9.9277797118296138E-2</v>
+        <v>0.19612612231534801</v>
       </c>
       <c r="K4">
-        <v>0.12859123949826309</v>
+        <v>0.2120407695560845</v>
       </c>
       <c r="L4">
-        <v>0.120883134786871</v>
+        <v>0.24076334244371791</v>
       </c>
       <c r="M4">
-        <v>0.19811139155647978</v>
+        <v>0.2515475077754965</v>
       </c>
       <c r="N4">
-        <v>0.19275881941213541</v>
+        <v>0.22804079980856531</v>
       </c>
       <c r="O4">
-        <v>0.16332418525123069</v>
+        <v>0.24612502923546858</v>
       </c>
       <c r="P4">
-        <v>0.13845818331804599</v>
+        <v>0.24122140464981048</v>
       </c>
       <c r="Q4">
-        <v>0.17321570969695821</v>
+        <v>0.25383203669113041</v>
       </c>
       <c r="R4">
-        <v>0.2311011628004816</v>
+        <v>0.27166616365594148</v>
       </c>
       <c r="S4">
-        <v>0.14675733461978502</v>
+        <v>0.2293876512998364</v>
       </c>
       <c r="T4">
-        <v>9.9394006227721363E-2</v>
+        <v>0.1350092828668254</v>
       </c>
       <c r="U4">
-        <v>0.17673245022317011</v>
+        <v>0.20668343356313848</v>
       </c>
       <c r="V4">
-        <v>1.839866574382585E-2</v>
+        <v>0.1208918472888901</v>
       </c>
       <c r="W4">
-        <v>0.1238525089555544</v>
+        <v>0.2060606107426603</v>
       </c>
       <c r="X4">
-        <v>1.250104770477016E-2</v>
+        <v>0.1022593244130014</v>
       </c>
       <c r="Y4">
-        <v>2.3547867286155183E-2</v>
+        <v>0.11364610358988639</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -2349,11 +2349,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2610,27 +2611,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95B8A76-94F3-412F-9855-4B93BB4C4C10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE34160-36D4-4F46-97A9-A281FB44CDD4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="28683373-984a-4841-9f0e-018f3f7bab1f"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6d4e152b-60f6-4719-8921-68b5b8011cde"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2655,9 +2646,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE34160-36D4-4F46-97A9-A281FB44CDD4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95B8A76-94F3-412F-9855-4B93BB4C4C10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="28683373-984a-4841-9f0e-018f3f7bab1f"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6d4e152b-60f6-4719-8921-68b5b8011cde"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/model/Inputs/inputs_RE.xlsx
+++ b/model/Inputs/inputs_RE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{495A37BE-6FBB-4E3C-92A2-55B475ABE098}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDC67725-A19D-4E07-80C6-EC90B674331D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -320,10 +320,6 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -760,10 +756,10 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>556</v>
+        <v>400</v>
       </c>
       <c r="C2">
-        <v>385</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1621,76 +1617,76 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.50966710862198827</v>
+        <v>0.55103020533172187</v>
       </c>
       <c r="C2">
-        <v>0.5378994808540265</v>
+        <v>0.49610429857327759</v>
       </c>
       <c r="D2">
-        <v>0.53090703423607699</v>
+        <v>0.47175502041968831</v>
       </c>
       <c r="E2">
-        <v>0.53124301708715971</v>
+        <v>0.54190573537941633</v>
       </c>
       <c r="F2">
-        <v>0.52153379679324718</v>
+        <v>0.60989323426304376</v>
       </c>
       <c r="G2">
-        <v>0.49426688993448104</v>
+        <v>0.65615698507344467</v>
       </c>
       <c r="H2">
-        <v>0.42588406065382994</v>
+        <v>0.57345733893247952</v>
       </c>
       <c r="I2">
-        <v>0.38927000806723039</v>
+        <v>0.52579297250377299</v>
       </c>
       <c r="J2">
-        <v>0.32784201041527922</v>
+        <v>0.45261476131671574</v>
       </c>
       <c r="K2">
-        <v>0.39403786103913829</v>
+        <v>0.55022462761245139</v>
       </c>
       <c r="L2">
-        <v>0.42387390011083459</v>
+        <v>0.58941603742496806</v>
       </c>
       <c r="M2">
-        <v>0.41429178637998687</v>
+        <v>0.57586558306818181</v>
       </c>
       <c r="N2">
-        <v>0.41261342373487581</v>
+        <v>0.57353265899147732</v>
       </c>
       <c r="O2">
-        <v>0.41384570399583948</v>
+        <v>0.57524552855421685</v>
       </c>
       <c r="P2">
-        <v>0.41587988599549158</v>
+        <v>0.57808248938817386</v>
       </c>
       <c r="Q2">
-        <v>0.39982959439825999</v>
+        <v>0.55576422468612374</v>
       </c>
       <c r="R2">
-        <v>0.38773501471725841</v>
+        <v>0.53896384453533031</v>
       </c>
       <c r="S2">
-        <v>0.3186474998936335</v>
+        <v>0.44292002485215048</v>
       </c>
       <c r="T2">
-        <v>0.25054140426885008</v>
+        <v>0.34825255193370169</v>
       </c>
       <c r="U2">
-        <v>0.27056497061016371</v>
+        <v>0.38160444029252077</v>
       </c>
       <c r="V2">
-        <v>0.36064017729795278</v>
+        <v>0.47419720332388365</v>
       </c>
       <c r="W2">
-        <v>0.39697265447803048</v>
+        <v>0.4877111717521122</v>
       </c>
       <c r="X2">
-        <v>0.42768970618440738</v>
+        <v>0.52533636824763186</v>
       </c>
       <c r="Y2">
-        <v>0.4793303803666743</v>
+        <v>0.57693786350230403</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
@@ -1698,76 +1694,76 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.21451117157625252</v>
+        <v>0.30086097636604769</v>
       </c>
       <c r="C3">
-        <v>0.201505708253541</v>
+        <v>0.33043288540182392</v>
       </c>
       <c r="D3">
-        <v>0.18470652041524671</v>
+        <v>0.27809402356071966</v>
       </c>
       <c r="E3">
-        <v>0.18225432239922348</v>
+        <v>0.30451730640166025</v>
       </c>
       <c r="F3">
-        <v>0.1554154603117506</v>
+        <v>9.6890092592592555E-2</v>
       </c>
       <c r="G3">
-        <v>0.1117803120003997</v>
+        <v>5.3708466145833411E-2</v>
       </c>
       <c r="H3">
-        <v>9.0519316070893294E-2</v>
+        <v>0.2408594801470588</v>
       </c>
       <c r="I3">
-        <v>3.6473810596522891E-3</v>
+        <v>0.24880595</v>
       </c>
       <c r="J3">
-        <v>6.4906675934941482E-3</v>
+        <v>0.31709406666666673</v>
       </c>
       <c r="K3">
-        <v>1.3591447442735459E-2</v>
+        <v>0.34460359743589747</v>
       </c>
       <c r="L3">
-        <v>2.2364190957251128E-2</v>
+        <v>0.34638594944968548</v>
       </c>
       <c r="M3">
-        <v>3.1440585337638952E-2</v>
+        <v>0.35533508480504583</v>
       </c>
       <c r="N3">
-        <v>8.5988232895579907E-3</v>
+        <v>0.32835428020833329</v>
       </c>
       <c r="O3">
-        <v>7.2333525303942922E-2</v>
+        <v>0.35649061111111108</v>
       </c>
       <c r="P3">
-        <v>1.866558683208901E-2</v>
+        <v>0.33493601853582561</v>
       </c>
       <c r="Q3">
-        <v>6.6216998886605011E-2</v>
+        <v>0.34995443521505382</v>
       </c>
       <c r="R3">
-        <v>2.0066803971457031E-2</v>
+        <v>0.36419875990990991</v>
       </c>
       <c r="S3">
-        <v>8.3773723157837349E-2</v>
+        <v>0.3688032323979592</v>
       </c>
       <c r="T3">
-        <v>0.1144162737037261</v>
+        <v>0.37649176670560752</v>
       </c>
       <c r="U3">
-        <v>0.16986397859008559</v>
+        <v>0.3969946268081761</v>
       </c>
       <c r="V3">
-        <v>0.20655493073070949</v>
+        <v>0.39245690752873558</v>
       </c>
       <c r="W3">
-        <v>0.22152122671408322</v>
+        <v>0.45282445143678174</v>
       </c>
       <c r="X3">
-        <v>0.20763276923213911</v>
+        <v>0.36701057704378137</v>
       </c>
       <c r="Y3">
-        <v>0.2348585481078552</v>
+        <v>0.39380200730040377</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -1775,76 +1771,76 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>8.005597698503418E-2</v>
+        <v>0.26698338071273048</v>
       </c>
       <c r="C4">
-        <v>7.7211791688954104E-2</v>
+        <v>0.2538515773604087</v>
       </c>
       <c r="D4">
-        <v>5.5918791628873997E-2</v>
+        <v>0.21363559324698039</v>
       </c>
       <c r="E4">
-        <v>1.0642524735926339E-2</v>
+        <v>0.1516221565352886</v>
       </c>
       <c r="F4">
-        <v>3.9543081047258954E-2</v>
+        <v>0.19534109746323072</v>
       </c>
       <c r="G4">
-        <v>8.6450810668165581E-2</v>
+        <v>0.26234729241111748</v>
       </c>
       <c r="H4">
-        <v>0.14607880221876421</v>
+        <v>0.27239182303155163</v>
       </c>
       <c r="I4">
-        <v>0.17308492085455379</v>
+        <v>0.30422873565173092</v>
       </c>
       <c r="J4">
-        <v>0.19612612231534801</v>
+        <v>0.31748855359849026</v>
       </c>
       <c r="K4">
-        <v>0.2120407695560845</v>
+        <v>0.32253314542633843</v>
       </c>
       <c r="L4">
-        <v>0.24076334244371791</v>
+        <v>0.3372116907030957</v>
       </c>
       <c r="M4">
-        <v>0.2515475077754965</v>
+        <v>0.3473144598690126</v>
       </c>
       <c r="N4">
-        <v>0.22804079980856531</v>
+        <v>0.31921386116308298</v>
       </c>
       <c r="O4">
-        <v>0.24612502923546858</v>
+        <v>0.34614134612960695</v>
       </c>
       <c r="P4">
-        <v>0.24122140464981048</v>
+        <v>0.344320010122869</v>
       </c>
       <c r="Q4">
-        <v>0.25383203669113041</v>
+        <v>0.37876250407361461</v>
       </c>
       <c r="R4">
-        <v>0.27166616365594148</v>
+        <v>0.42284536009515272</v>
       </c>
       <c r="S4">
-        <v>0.2293876512998364</v>
+        <v>0.40845596142417745</v>
       </c>
       <c r="T4">
-        <v>0.1350092828668254</v>
+        <v>0.33580565438096399</v>
       </c>
       <c r="U4">
-        <v>0.20668343356313848</v>
+        <v>0.45075077460331781</v>
       </c>
       <c r="V4">
-        <v>0.1208918472888901</v>
+        <v>0.35718453807084516</v>
       </c>
       <c r="W4">
-        <v>0.2060606107426603</v>
+        <v>0.45735928394765896</v>
       </c>
       <c r="X4">
-        <v>0.1022593244130014</v>
+        <v>0.33068006431882202</v>
       </c>
       <c r="Y4">
-        <v>0.11364610358988639</v>
+        <v>0.32997560070809001</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -2022,76 +2018,76 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.6499526881720431</v>
+        <v>0.64928703812316724</v>
       </c>
       <c r="C2">
-        <v>0.67091338709677428</v>
+        <v>0.66732468936678602</v>
       </c>
       <c r="D2">
-        <v>0.6677365591397848</v>
+        <v>0.66392413381123061</v>
       </c>
       <c r="E2">
-        <v>0.66065053763440862</v>
+        <v>0.66067230368198115</v>
       </c>
       <c r="F2">
-        <v>0.65670430107526878</v>
+        <v>0.6516750081459759</v>
       </c>
       <c r="G2">
-        <v>0.63447311827956987</v>
+        <v>0.6274401759530791</v>
       </c>
       <c r="H2">
-        <v>0.60750537634408597</v>
+        <v>0.60505088325652845</v>
       </c>
       <c r="I2">
-        <v>0.62390860215053756</v>
+        <v>0.62057450076804921</v>
       </c>
       <c r="J2">
-        <v>0.68743172043010747</v>
+        <v>0.68841755941220761</v>
       </c>
       <c r="K2">
-        <v>0.7462182795698924</v>
+        <v>0.74890578690127074</v>
       </c>
       <c r="L2">
-        <v>0.85605000000000009</v>
+        <v>0.86696318199920364</v>
       </c>
       <c r="M2">
-        <v>1.0262306451612901</v>
+        <v>1.025523755475906</v>
       </c>
       <c r="N2">
-        <v>1.1167392473118281</v>
+        <v>1.119878634010355</v>
       </c>
       <c r="O2">
-        <v>1.1836376344086019</v>
+        <v>1.186166109119873</v>
       </c>
       <c r="P2">
-        <v>1.027217741935484</v>
+        <v>1.0251870768618081</v>
       </c>
       <c r="Q2">
-        <v>0.8889456989247313</v>
+        <v>0.88724254992319529</v>
       </c>
       <c r="R2">
-        <v>0.7538978494623656</v>
+        <v>0.74724487327188949</v>
       </c>
       <c r="S2">
-        <v>0.50274516129032254</v>
+        <v>0.49384039938556074</v>
       </c>
       <c r="T2">
-        <v>0.41429516129032262</v>
+        <v>0.40557127496159762</v>
       </c>
       <c r="U2">
-        <v>0.4041424731182795</v>
+        <v>0.3961019393241168</v>
       </c>
       <c r="V2">
-        <v>0.56056989247311817</v>
+        <v>0.55229350856232573</v>
       </c>
       <c r="W2">
-        <v>0.62054930107526873</v>
+        <v>0.61662600006627233</v>
       </c>
       <c r="X2">
-        <v>0.64192150537634407</v>
+        <v>0.63838621351766522</v>
       </c>
       <c r="Y2">
-        <v>0.62158602150537634</v>
+        <v>0.62185117302052784</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
@@ -2099,76 +2095,76 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.21790277777777781</v>
+        <v>0.18475517241379311</v>
       </c>
       <c r="C3">
-        <v>0.1977038888888889</v>
+        <v>0.16214137931034481</v>
       </c>
       <c r="D3">
-        <v>0.18487999999999999</v>
+        <v>0.1448298245614035</v>
       </c>
       <c r="E3">
-        <v>0.1786611111111111</v>
+        <v>0.1433526315789474</v>
       </c>
       <c r="F3">
-        <v>0.1766422222222222</v>
+        <v>0.127</v>
       </c>
       <c r="G3">
-        <v>0.18018061111111108</v>
+        <v>0.13865183333333328</v>
       </c>
       <c r="H3">
-        <v>0.18553142722222218</v>
+        <v>0.14666094833333329</v>
       </c>
       <c r="I3">
-        <v>0.26766836438888891</v>
+        <v>0.25572342649999996</v>
       </c>
       <c r="J3">
-        <v>0.35331903883333332</v>
+        <v>0.30850378316666671</v>
       </c>
       <c r="K3">
-        <v>0.42253938000000002</v>
+        <v>0.33145980666666669</v>
       </c>
       <c r="L3">
-        <v>0.49076894211111105</v>
+        <v>0.38475182633333332</v>
       </c>
       <c r="M3">
-        <v>0.52016991500000009</v>
+        <v>0.31717974500000001</v>
       </c>
       <c r="N3">
-        <v>0.56216287194444436</v>
+        <v>0.32032861583333327</v>
       </c>
       <c r="O3">
-        <v>0.56496133111111113</v>
+        <v>0.47160732666666672</v>
       </c>
       <c r="P3">
-        <v>0.48988244055555563</v>
+        <v>0.36909232166666667</v>
       </c>
       <c r="Q3">
-        <v>0.39801944444444437</v>
+        <v>0.25795499999999999</v>
       </c>
       <c r="R3">
-        <v>0.37564677777777777</v>
+        <v>0.35210199999999997</v>
       </c>
       <c r="S3">
-        <v>0.26654516666666672</v>
+        <v>0.25645883333333341</v>
       </c>
       <c r="T3">
-        <v>0.24320322222222218</v>
+        <v>0.23295133333333332</v>
       </c>
       <c r="U3">
-        <v>0.25915172105555551</v>
+        <v>0.26914016316666656</v>
       </c>
       <c r="V3">
-        <v>0.2592240844444445</v>
+        <v>0.30327129655172408</v>
       </c>
       <c r="W3">
-        <v>0.25418348333333329</v>
+        <v>0.28226081034482758</v>
       </c>
       <c r="X3">
-        <v>0.24293875555555558</v>
+        <v>0.2358750175438597</v>
       </c>
       <c r="Y3">
-        <v>0.2245986888888889</v>
+        <v>0.19264757142857142</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -2176,22 +2172,22 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0.29218918757467149</v>
+        <v>0.29215451158738037</v>
       </c>
       <c r="C4">
-        <v>0.26297022188086699</v>
+        <v>0.26282476061785742</v>
       </c>
       <c r="D4">
-        <v>0.25247546594982079</v>
+        <v>0.2526449428776808</v>
       </c>
       <c r="E4">
-        <v>0.2583069583376002</v>
+        <v>0.25855449801810787</v>
       </c>
       <c r="F4">
-        <v>0.26884988180576891</v>
+        <v>0.26913843615055588</v>
       </c>
       <c r="G4">
-        <v>0.25970625277351095</v>
+        <v>0.25942136433014545</v>
       </c>
       <c r="H4">
         <v>0.27721292072025938</v>
@@ -2203,7 +2199,7 @@
         <v>0.37542224782386069</v>
       </c>
       <c r="K4">
-        <v>0.41070786546338967</v>
+        <v>0.4110577215066355</v>
       </c>
       <c r="L4">
         <v>0.4224946364567333</v>
@@ -2212,40 +2208,40 @@
         <v>0.41664988095238104</v>
       </c>
       <c r="N4">
-        <v>0.4182775402841783</v>
+        <v>0.41653241131067803</v>
       </c>
       <c r="O4">
-        <v>0.37095263056835642</v>
+        <v>0.36737431814302779</v>
       </c>
       <c r="P4">
-        <v>0.33604372759856632</v>
+        <v>0.33236718936678605</v>
       </c>
       <c r="Q4">
-        <v>0.34589174347158219</v>
+        <v>0.34262816648899413</v>
       </c>
       <c r="R4">
-        <v>0.35881936763952887</v>
+        <v>0.35694885820889249</v>
       </c>
       <c r="S4">
-        <v>0.36808729749103952</v>
+        <v>0.36824177190199192</v>
       </c>
       <c r="T4">
-        <v>0.40537927345110092</v>
+        <v>0.40531298283473099</v>
       </c>
       <c r="U4">
-        <v>0.42410566717869935</v>
+        <v>0.42446832068360574</v>
       </c>
       <c r="V4">
-        <v>0.43678193292370709</v>
+        <v>0.43705531238195972</v>
       </c>
       <c r="W4">
-        <v>0.41374089221710186</v>
+        <v>0.4143171390301098</v>
       </c>
       <c r="X4">
-        <v>0.37375091525857657</v>
+        <v>0.37375051864603331</v>
       </c>
       <c r="Y4">
-        <v>0.34653108678955447</v>
+        <v>0.3463776522754351</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">

--- a/model/Inputs/inputs_RE.xlsx
+++ b/model/Inputs/inputs_RE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDC67725-A19D-4E07-80C6-EC90B674331D}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9F6A536-4F5A-401B-914D-3C4166CD7987}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -1706,10 +1706,10 @@
         <v>0.30451730640166025</v>
       </c>
       <c r="F3">
-        <v>9.6890092592592555E-2</v>
+        <v>0.28329803098345968</v>
       </c>
       <c r="G3">
-        <v>5.3708466145833411E-2</v>
+        <v>0.26207875556525934</v>
       </c>
       <c r="H3">
         <v>0.2408594801470588</v>
@@ -1780,7 +1780,7 @@
         <v>0.21363559324698039</v>
       </c>
       <c r="E4">
-        <v>0.1516221565352886</v>
+        <v>0.20448834535510552</v>
       </c>
       <c r="F4">
         <v>0.19534109746323072</v>
@@ -2345,6 +2345,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2353,7 +2361,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D835CF4C7D56B243BA013D4D2E10914B" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e645ef68b9493f2ee8bae9e534bc24f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6d4e152b-60f6-4719-8921-68b5b8011cde" xmlns:ns4="28683373-984a-4841-9f0e-018f3f7bab1f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a06da6e71fc3d3bdf7cbe176c2a8afa1" ns3:_="" ns4:_="">
     <xsd:import namespace="6d4e152b-60f6-4719-8921-68b5b8011cde"/>
@@ -2606,15 +2614,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95B8A76-94F3-412F-9855-4B93BB4C4C10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="28683373-984a-4841-9f0e-018f3f7bab1f"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6d4e152b-60f6-4719-8921-68b5b8011cde"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE34160-36D4-4F46-97A9-A281FB44CDD4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2622,7 +2639,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCE4FBA5-6C26-4B97-9218-92B658F853C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2639,21 +2656,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95B8A76-94F3-412F-9855-4B93BB4C4C10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="28683373-984a-4841-9f0e-018f3f7bab1f"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="6d4e152b-60f6-4719-8921-68b5b8011cde"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/model/Inputs/inputs_RE.xlsx
+++ b/model/Inputs/inputs_RE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailaub-my.sharepoint.com/personal/mo10_aub_edu_lb/Documents/3-Research/Elsa/Model 1/Github/Model-1/model/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9F6A536-4F5A-401B-914D-3C4166CD7987}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="6_{7DA8CDEE-914B-4384-BE83-347F050180D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C94A9A12-BDD7-56FD-8819-BCD3023FE1FD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="1" r:id="rId1"/>
@@ -2345,20 +2345,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6d4e152b-60f6-4719-8921-68b5b8011cde" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2615,6 +2615,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE34160-36D4-4F46-97A9-A281FB44CDD4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95B8A76-94F3-412F-9855-4B93BB4C4C10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2627,14 +2635,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE34160-36D4-4F46-97A9-A281FB44CDD4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
